--- a/Result/profitability/4114.xlsx
+++ b/Result/profitability/4114.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.06</v>
       </c>
       <c r="M2" t="n">
-        <v>0.35875</v>
+        <v>0.365</v>
       </c>
       <c r="N2" t="n">
-        <v>43.1025</v>
+        <v>42.56625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.03</v>
       </c>
       <c r="M3" t="n">
-        <v>0.30625</v>
+        <v>0.32</v>
       </c>
       <c r="N3" t="n">
-        <v>43.33625</v>
+        <v>42.85875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.05</v>
       </c>
       <c r="M4" t="n">
-        <v>0.27125</v>
+        <v>0.26625</v>
       </c>
       <c r="N4" t="n">
-        <v>43.9525</v>
+        <v>43.28</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
         <v>0.165</v>
       </c>
       <c r="N5" t="n">
-        <v>44.0375</v>
+        <v>43.275</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.2</v>
       </c>
       <c r="M6" t="n">
-        <v>0.135</v>
+        <v>0.13875</v>
       </c>
       <c r="N6" t="n">
-        <v>44.4</v>
+        <v>43.99375</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.96</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.03624999999999998</v>
+        <v>-0.02874999999999998</v>
       </c>
       <c r="N7" t="n">
-        <v>45.17375</v>
+        <v>44.755</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.18</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.06124999999999999</v>
+        <v>-0.05374999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>45.8225</v>
+        <v>45.37625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1521,7 +1521,7 @@
         <v>-0.11625</v>
       </c>
       <c r="N9" t="n">
-        <v>45.8925</v>
+        <v>45.89250000000001</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -1899,7 +1899,7 @@
         <v>0.12</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.05124999999999998</v>
+        <v>-0.05124999999999999</v>
       </c>
       <c r="N12" t="n">
         <v>46.1475</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4114</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1922</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1177</v>
+      </c>
+      <c r="E75" t="n">
+        <v>745</v>
+      </c>
+      <c r="F75" t="n">
+        <v>38.76</v>
+      </c>
+      <c r="G75" t="n">
+        <v>224</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>11.65%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>27</v>
+      </c>
+      <c r="J75" t="n">
+        <v>251</v>
+      </c>
+      <c r="K75" t="n">
+        <v>239</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.40625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>42.48</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.1578947368421053</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-3.57</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.08433734939759041</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-6.100000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1359786000891663</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
